--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/08,26/24,08,26 Останкино КИ и ЗПФ/дв 24,08,26 лгрсч ост ки.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/08,26/24,08,26 Останкино КИ и ЗПФ/дв 24,08,26 лгрсч ост ки.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\08,26\24,08,26 Останкино КИ и ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E34FAA1-26BB-4E65-A4C0-FB716F565925}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8E9AAD7-E0F8-41C6-9C5F-B4B327EBE131}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AH$105</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -9434,7 +9434,10 @@
         <f>SUM(AH6:AH500)</f>
         <v>5498.9800000000005</v>
       </c>
-      <c r="AI5" s="12"/>
+      <c r="AI5" s="3">
+        <f>SUM(AI6:AI500)</f>
+        <v>1508.7516000000005</v>
+      </c>
       <c r="AJ5" s="12"/>
       <c r="AK5" s="12"/>
       <c r="AL5" s="12"/>
@@ -9550,7 +9553,10 @@
         <f>G6*R6</f>
         <v>13.200000000000001</v>
       </c>
-      <c r="AI6" s="12"/>
+      <c r="AI6" s="12">
+        <f>P6*G6</f>
+        <v>8.08</v>
+      </c>
       <c r="AJ6" s="12"/>
       <c r="AK6" s="12"/>
       <c r="AL6" s="12"/>
@@ -9669,7 +9675,10 @@
         <f t="shared" ref="AH7:AH70" si="6">G7*R7</f>
         <v>30</v>
       </c>
-      <c r="AI7" s="12"/>
+      <c r="AI7" s="12">
+        <f t="shared" ref="AI7:AI70" si="7">P7*G7</f>
+        <v>2.5045999999999999</v>
+      </c>
       <c r="AJ7" s="12"/>
       <c r="AK7" s="12"/>
       <c r="AL7" s="12"/>
@@ -9731,11 +9740,11 @@
         <v>10.4</v>
       </c>
       <c r="Q8" s="4">
-        <f t="shared" ref="Q8:Q16" si="7">15*P8-O8-F8</f>
+        <f t="shared" ref="Q8:Q16" si="8">15*P8-O8-F8</f>
         <v>10</v>
       </c>
       <c r="R8" s="4">
-        <f t="shared" ref="R7:R70" si="8">ROUND(Q8,0)</f>
+        <f t="shared" ref="R8:R70" si="9">ROUND(Q8,0)</f>
         <v>10</v>
       </c>
       <c r="S8" s="16"/>
@@ -9785,7 +9794,10 @@
         <f t="shared" si="6"/>
         <v>2.5</v>
       </c>
-      <c r="AI8" s="12"/>
+      <c r="AI8" s="12">
+        <f t="shared" si="7"/>
+        <v>2.6</v>
+      </c>
       <c r="AJ8" s="12"/>
       <c r="AK8" s="12"/>
       <c r="AL8" s="12"/>
@@ -9850,7 +9862,7 @@
       </c>
       <c r="Q9" s="4"/>
       <c r="R9" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S9" s="16"/>
@@ -9898,7 +9910,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI9" s="12"/>
+      <c r="AI9" s="12">
+        <f t="shared" si="7"/>
+        <v>112.44500000000001</v>
+      </c>
       <c r="AJ9" s="12"/>
       <c r="AK9" s="12"/>
       <c r="AL9" s="12"/>
@@ -9961,7 +9976,7 @@
       </c>
       <c r="Q10" s="4"/>
       <c r="R10" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S10" s="16"/>
@@ -10011,7 +10026,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI10" s="12"/>
+      <c r="AI10" s="12">
+        <f t="shared" si="7"/>
+        <v>2.2122000000000002</v>
+      </c>
       <c r="AJ10" s="12"/>
       <c r="AK10" s="12"/>
       <c r="AL10" s="12"/>
@@ -10075,11 +10093,11 @@
         <v>45.863799999999998</v>
       </c>
       <c r="Q11" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>182.11399999999998</v>
       </c>
       <c r="R11" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>182</v>
       </c>
       <c r="S11" s="16"/>
@@ -10129,7 +10147,10 @@
         <f t="shared" si="6"/>
         <v>182</v>
       </c>
-      <c r="AI11" s="12"/>
+      <c r="AI11" s="12">
+        <f t="shared" si="7"/>
+        <v>45.863799999999998</v>
+      </c>
       <c r="AJ11" s="12"/>
       <c r="AK11" s="12"/>
       <c r="AL11" s="12"/>
@@ -10193,7 +10214,7 @@
         <v>53.7774</v>
       </c>
       <c r="Q12" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>206.98500000000007</v>
       </c>
       <c r="R12" s="4">
@@ -10251,7 +10272,10 @@
         <f t="shared" si="6"/>
         <v>307</v>
       </c>
-      <c r="AI12" s="12"/>
+      <c r="AI12" s="12">
+        <f t="shared" si="7"/>
+        <v>53.7774</v>
+      </c>
       <c r="AJ12" s="12"/>
       <c r="AK12" s="12"/>
       <c r="AL12" s="12"/>
@@ -10314,7 +10338,7 @@
       </c>
       <c r="Q13" s="4"/>
       <c r="R13" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S13" s="16"/>
@@ -10364,7 +10388,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI13" s="12"/>
+      <c r="AI13" s="12">
+        <f t="shared" si="7"/>
+        <v>1.8</v>
+      </c>
       <c r="AJ13" s="12"/>
       <c r="AK13" s="12"/>
       <c r="AL13" s="12"/>
@@ -10483,7 +10510,10 @@
         <f t="shared" si="6"/>
         <v>50</v>
       </c>
-      <c r="AI14" s="12"/>
+      <c r="AI14" s="12">
+        <f t="shared" si="7"/>
+        <v>7.6433999999999997</v>
+      </c>
       <c r="AJ14" s="12"/>
       <c r="AK14" s="12"/>
       <c r="AL14" s="12"/>
@@ -10551,7 +10581,7 @@
         <v>75.600000000000023</v>
       </c>
       <c r="R15" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>76</v>
       </c>
       <c r="S15" s="16"/>
@@ -10601,7 +10631,10 @@
         <f t="shared" si="6"/>
         <v>19</v>
       </c>
-      <c r="AI15" s="12"/>
+      <c r="AI15" s="12">
+        <f t="shared" si="7"/>
+        <v>9.6</v>
+      </c>
       <c r="AJ15" s="12"/>
       <c r="AK15" s="12"/>
       <c r="AL15" s="12"/>
@@ -10663,11 +10696,11 @@
         <v>18.600000000000001</v>
       </c>
       <c r="Q16" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>27</v>
       </c>
       <c r="R16" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>27</v>
       </c>
       <c r="S16" s="16"/>
@@ -10715,7 +10748,10 @@
         <f t="shared" si="6"/>
         <v>10.8</v>
       </c>
-      <c r="AI16" s="12"/>
+      <c r="AI16" s="12">
+        <f t="shared" si="7"/>
+        <v>7.4400000000000013</v>
+      </c>
       <c r="AJ16" s="12"/>
       <c r="AK16" s="12"/>
       <c r="AL16" s="12"/>
@@ -10829,7 +10865,10 @@
         <f t="shared" si="6"/>
         <v>150</v>
       </c>
-      <c r="AI17" s="12"/>
+      <c r="AI17" s="12">
+        <f t="shared" si="7"/>
+        <v>50.552800000000005</v>
+      </c>
       <c r="AJ17" s="12"/>
       <c r="AK17" s="12"/>
       <c r="AL17" s="12"/>
@@ -10890,7 +10929,7 @@
       </c>
       <c r="Q18" s="10"/>
       <c r="R18" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S18" s="16"/>
@@ -10938,7 +10977,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI18" s="12"/>
+      <c r="AI18" s="12">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AJ18" s="12"/>
       <c r="AK18" s="12"/>
       <c r="AL18" s="12"/>
@@ -11003,7 +11045,7 @@
       </c>
       <c r="Q19" s="4"/>
       <c r="R19" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S19" s="16"/>
@@ -11053,7 +11095,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI19" s="12"/>
+      <c r="AI19" s="12">
+        <f t="shared" si="7"/>
+        <v>6.8586</v>
+      </c>
       <c r="AJ19" s="12"/>
       <c r="AK19" s="12"/>
       <c r="AL19" s="12"/>
@@ -11116,7 +11161,7 @@
       </c>
       <c r="Q20" s="4"/>
       <c r="R20" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S20" s="16"/>
@@ -11164,7 +11209,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI20" s="12"/>
+      <c r="AI20" s="12">
+        <f t="shared" si="7"/>
+        <v>4.16</v>
+      </c>
       <c r="AJ20" s="12"/>
       <c r="AK20" s="12"/>
       <c r="AL20" s="12"/>
@@ -11228,11 +11276,11 @@
         <v>44.343599999999995</v>
       </c>
       <c r="Q21" s="4">
-        <f t="shared" ref="Q21:Q29" si="9">15*P21-O21-F21</f>
+        <f t="shared" ref="Q21:Q29" si="10">15*P21-O21-F21</f>
         <v>173.90899999999988</v>
       </c>
       <c r="R21" s="4">
-        <f t="shared" ref="R21:R24" si="10">ROUND(S21,0)</f>
+        <f t="shared" ref="R21:R24" si="11">ROUND(S21,0)</f>
         <v>250</v>
       </c>
       <c r="S21" s="16">
@@ -11286,7 +11334,10 @@
         <f t="shared" si="6"/>
         <v>250</v>
       </c>
-      <c r="AI21" s="12"/>
+      <c r="AI21" s="12">
+        <f t="shared" si="7"/>
+        <v>44.343599999999995</v>
+      </c>
       <c r="AJ21" s="12"/>
       <c r="AK21" s="12"/>
       <c r="AL21" s="12"/>
@@ -11348,11 +11399,11 @@
         <v>95.4</v>
       </c>
       <c r="Q22" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>445</v>
       </c>
       <c r="R22" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>600</v>
       </c>
       <c r="S22" s="16">
@@ -11408,7 +11459,10 @@
         <f t="shared" si="6"/>
         <v>132</v>
       </c>
-      <c r="AI22" s="12"/>
+      <c r="AI22" s="12">
+        <f t="shared" si="7"/>
+        <v>20.988000000000003</v>
+      </c>
       <c r="AJ22" s="12"/>
       <c r="AK22" s="12"/>
       <c r="AL22" s="12"/>
@@ -11472,7 +11526,7 @@
         <v>6.0042</v>
       </c>
       <c r="Q23" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>19.315000000000001</v>
       </c>
       <c r="R23" s="4">
@@ -11531,7 +11585,10 @@
         <f t="shared" si="6"/>
         <v>40</v>
       </c>
-      <c r="AI23" s="12"/>
+      <c r="AI23" s="12">
+        <f t="shared" si="7"/>
+        <v>6.0042</v>
+      </c>
       <c r="AJ23" s="12"/>
       <c r="AK23" s="12"/>
       <c r="AL23" s="12"/>
@@ -11593,11 +11650,11 @@
         <v>24.778200000000002</v>
       </c>
       <c r="Q24" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>15.917000000000002</v>
       </c>
       <c r="R24" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>60</v>
       </c>
       <c r="S24" s="16">
@@ -11651,7 +11708,10 @@
         <f t="shared" si="6"/>
         <v>60</v>
       </c>
-      <c r="AI24" s="12"/>
+      <c r="AI24" s="12">
+        <f t="shared" si="7"/>
+        <v>24.778200000000002</v>
+      </c>
       <c r="AJ24" s="12"/>
       <c r="AK24" s="12"/>
       <c r="AL24" s="12"/>
@@ -11716,7 +11776,7 @@
       </c>
       <c r="Q25" s="4"/>
       <c r="R25" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S25" s="16"/>
@@ -11764,7 +11824,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI25" s="12"/>
+      <c r="AI25" s="12">
+        <f t="shared" si="7"/>
+        <v>4.032</v>
+      </c>
       <c r="AJ25" s="12"/>
       <c r="AK25" s="12"/>
       <c r="AL25" s="12"/>
@@ -11828,11 +11891,11 @@
         <v>39.200000000000003</v>
       </c>
       <c r="Q26" s="4">
+        <f t="shared" si="10"/>
+        <v>224</v>
+      </c>
+      <c r="R26" s="4">
         <f t="shared" si="9"/>
-        <v>224</v>
-      </c>
-      <c r="R26" s="4">
-        <f t="shared" si="8"/>
         <v>224</v>
       </c>
       <c r="S26" s="16"/>
@@ -11882,7 +11945,10 @@
         <f t="shared" si="6"/>
         <v>20.16</v>
       </c>
-      <c r="AI26" s="12"/>
+      <c r="AI26" s="12">
+        <f t="shared" si="7"/>
+        <v>3.528</v>
+      </c>
       <c r="AJ26" s="12"/>
       <c r="AK26" s="12"/>
       <c r="AL26" s="12"/>
@@ -11946,11 +12012,11 @@
         <v>32.200000000000003</v>
       </c>
       <c r="Q27" s="4">
+        <f t="shared" si="10"/>
+        <v>207.00000000000006</v>
+      </c>
+      <c r="R27" s="4">
         <f t="shared" si="9"/>
-        <v>207.00000000000006</v>
-      </c>
-      <c r="R27" s="4">
-        <f t="shared" si="8"/>
         <v>207</v>
       </c>
       <c r="S27" s="16"/>
@@ -11998,7 +12064,10 @@
         <f t="shared" si="6"/>
         <v>31.049999999999997</v>
       </c>
-      <c r="AI27" s="12"/>
+      <c r="AI27" s="12">
+        <f t="shared" si="7"/>
+        <v>4.83</v>
+      </c>
       <c r="AJ27" s="12"/>
       <c r="AK27" s="12"/>
       <c r="AL27" s="12"/>
@@ -12062,11 +12131,11 @@
         <v>86.089399999999998</v>
       </c>
       <c r="Q28" s="4">
+        <f t="shared" si="10"/>
+        <v>232.3609999999999</v>
+      </c>
+      <c r="R28" s="4">
         <f t="shared" si="9"/>
-        <v>232.3609999999999</v>
-      </c>
-      <c r="R28" s="4">
-        <f t="shared" si="8"/>
         <v>232</v>
       </c>
       <c r="S28" s="16"/>
@@ -12114,7 +12183,10 @@
         <f t="shared" si="6"/>
         <v>232</v>
       </c>
-      <c r="AI28" s="12"/>
+      <c r="AI28" s="12">
+        <f t="shared" si="7"/>
+        <v>86.089399999999998</v>
+      </c>
       <c r="AJ28" s="12"/>
       <c r="AK28" s="12"/>
       <c r="AL28" s="12"/>
@@ -12178,11 +12250,11 @@
         <v>46.4</v>
       </c>
       <c r="Q29" s="4">
+        <f t="shared" si="10"/>
+        <v>56</v>
+      </c>
+      <c r="R29" s="4">
         <f t="shared" si="9"/>
-        <v>56</v>
-      </c>
-      <c r="R29" s="4">
-        <f t="shared" si="8"/>
         <v>56</v>
       </c>
       <c r="S29" s="16"/>
@@ -12232,7 +12304,10 @@
         <f t="shared" si="6"/>
         <v>22.400000000000002</v>
       </c>
-      <c r="AI29" s="12"/>
+      <c r="AI29" s="12">
+        <f t="shared" si="7"/>
+        <v>18.559999999999999</v>
+      </c>
       <c r="AJ29" s="12"/>
       <c r="AK29" s="12"/>
       <c r="AL29" s="12"/>
@@ -12297,7 +12372,7 @@
       </c>
       <c r="Q30" s="4"/>
       <c r="R30" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S30" s="16"/>
@@ -12347,7 +12422,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI30" s="12"/>
+      <c r="AI30" s="12">
+        <f t="shared" si="7"/>
+        <v>18</v>
+      </c>
       <c r="AJ30" s="12"/>
       <c r="AK30" s="12"/>
       <c r="AL30" s="12"/>
@@ -12408,7 +12486,7 @@
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S31" s="16"/>
@@ -12458,7 +12536,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI31" s="12"/>
+      <c r="AI31" s="12">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AJ31" s="12"/>
       <c r="AK31" s="12"/>
       <c r="AL31" s="12"/>
@@ -12526,7 +12607,7 @@
         <v>321.19999999999993</v>
       </c>
       <c r="R32" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>321</v>
       </c>
       <c r="S32" s="16"/>
@@ -12576,7 +12657,10 @@
         <f t="shared" si="6"/>
         <v>128.4</v>
       </c>
-      <c r="AI32" s="12"/>
+      <c r="AI32" s="12">
+        <f t="shared" si="7"/>
+        <v>17.12</v>
+      </c>
       <c r="AJ32" s="12"/>
       <c r="AK32" s="12"/>
       <c r="AL32" s="12"/>
@@ -12631,7 +12715,7 @@
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S33" s="16"/>
@@ -12681,7 +12765,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI33" s="12"/>
+      <c r="AI33" s="12">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AJ33" s="12"/>
       <c r="AK33" s="12"/>
       <c r="AL33" s="12"/>
@@ -12742,7 +12829,7 @@
       </c>
       <c r="Q34" s="10"/>
       <c r="R34" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S34" s="16"/>
@@ -12792,7 +12879,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI34" s="12"/>
+      <c r="AI34" s="12">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AJ34" s="12"/>
       <c r="AK34" s="12"/>
       <c r="AL34" s="12"/>
@@ -12859,7 +12949,7 @@
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S35" s="16"/>
@@ -12909,7 +12999,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI35" s="12"/>
+      <c r="AI35" s="12">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AJ35" s="12"/>
       <c r="AK35" s="12"/>
       <c r="AL35" s="12"/>
@@ -12974,7 +13067,7 @@
       </c>
       <c r="Q36" s="4"/>
       <c r="R36" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S36" s="16"/>
@@ -13022,7 +13115,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI36" s="12"/>
+      <c r="AI36" s="12">
+        <f t="shared" si="7"/>
+        <v>6.72</v>
+      </c>
       <c r="AJ36" s="12"/>
       <c r="AK36" s="12"/>
       <c r="AL36" s="12"/>
@@ -13086,11 +13182,11 @@
         <v>19.841200000000001</v>
       </c>
       <c r="Q37" s="4">
-        <f t="shared" ref="Q37:Q52" si="11">15*P37-O37-F37</f>
+        <f t="shared" ref="Q37:Q52" si="12">15*P37-O37-F37</f>
         <v>87.651999999999987</v>
       </c>
       <c r="R37" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>88</v>
       </c>
       <c r="S37" s="16"/>
@@ -13138,7 +13234,10 @@
         <f t="shared" si="6"/>
         <v>88</v>
       </c>
-      <c r="AI37" s="12"/>
+      <c r="AI37" s="12">
+        <f t="shared" si="7"/>
+        <v>19.841200000000001</v>
+      </c>
       <c r="AJ37" s="12"/>
       <c r="AK37" s="12"/>
       <c r="AL37" s="12"/>
@@ -13187,7 +13286,7 @@
         <v>80.099999999999994</v>
       </c>
       <c r="L38" s="12">
-        <f t="shared" ref="L38:L69" si="12">E38-K38</f>
+        <f t="shared" ref="L38:L69" si="13">E38-K38</f>
         <v>-2.6259999999999906</v>
       </c>
       <c r="M38" s="12"/>
@@ -13196,15 +13295,15 @@
         <v>145</v>
       </c>
       <c r="P38" s="12">
-        <f t="shared" ref="P38:P69" si="13">E38/5</f>
+        <f t="shared" ref="P38:P69" si="14">E38/5</f>
         <v>15.494800000000001</v>
       </c>
       <c r="Q38" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>32.645000000000024</v>
       </c>
       <c r="R38" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>33</v>
       </c>
       <c r="S38" s="16"/>
@@ -13214,7 +13313,7 @@
         <v>15.022910912047911</v>
       </c>
       <c r="V38" s="12">
-        <f t="shared" ref="V38:V69" si="14">(F38+O38)/P38</f>
+        <f t="shared" ref="V38:V69" si="15">(F38+O38)/P38</f>
         <v>12.893164158298266</v>
       </c>
       <c r="W38" s="12">
@@ -13252,7 +13351,10 @@
         <f t="shared" si="6"/>
         <v>33</v>
       </c>
-      <c r="AI38" s="12"/>
+      <c r="AI38" s="12">
+        <f t="shared" si="7"/>
+        <v>15.494800000000001</v>
+      </c>
       <c r="AJ38" s="12"/>
       <c r="AK38" s="12"/>
       <c r="AL38" s="12"/>
@@ -13303,7 +13405,7 @@
         <v>106.7</v>
       </c>
       <c r="L39" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-4.8800000000000097</v>
       </c>
       <c r="M39" s="12"/>
@@ -13312,15 +13414,15 @@
         <v>236</v>
       </c>
       <c r="P39" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>20.363999999999997</v>
       </c>
       <c r="Q39" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>39.575999999999979</v>
       </c>
       <c r="R39" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>40</v>
       </c>
       <c r="S39" s="16"/>
@@ -13330,7 +13432,7 @@
         <v>15.020821056766847</v>
       </c>
       <c r="V39" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>13.056570418385389</v>
       </c>
       <c r="W39" s="12">
@@ -13368,7 +13470,10 @@
         <f t="shared" si="6"/>
         <v>40</v>
       </c>
-      <c r="AI39" s="12"/>
+      <c r="AI39" s="12">
+        <f t="shared" si="7"/>
+        <v>20.363999999999997</v>
+      </c>
       <c r="AJ39" s="12"/>
       <c r="AK39" s="12"/>
       <c r="AL39" s="12"/>
@@ -13407,7 +13512,7 @@
       <c r="J40" s="12"/>
       <c r="K40" s="12"/>
       <c r="L40" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="M40" s="12"/>
@@ -13416,14 +13521,14 @@
         <v>0</v>
       </c>
       <c r="P40" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Q40" s="4">
         <v>300</v>
       </c>
       <c r="R40" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>300</v>
       </c>
       <c r="S40" s="16"/>
@@ -13433,7 +13538,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="V40" s="12" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W40" s="12">
@@ -13473,7 +13578,10 @@
         <f t="shared" si="6"/>
         <v>105</v>
       </c>
-      <c r="AI40" s="12"/>
+      <c r="AI40" s="12">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AJ40" s="12"/>
       <c r="AK40" s="12"/>
       <c r="AL40" s="12"/>
@@ -13522,7 +13630,7 @@
         <v>143.30000000000001</v>
       </c>
       <c r="L41" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-7.4780000000000086</v>
       </c>
       <c r="M41" s="12"/>
@@ -13531,12 +13639,12 @@
         <v>350</v>
       </c>
       <c r="P41" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>27.164400000000001</v>
       </c>
       <c r="Q41" s="4"/>
       <c r="R41" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S41" s="16"/>
@@ -13546,7 +13654,7 @@
         <v>17.552090235749731</v>
       </c>
       <c r="V41" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>17.552090235749731</v>
       </c>
       <c r="W41" s="12">
@@ -13584,7 +13692,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI41" s="12"/>
+      <c r="AI41" s="12">
+        <f t="shared" si="7"/>
+        <v>27.164400000000001</v>
+      </c>
       <c r="AJ41" s="12"/>
       <c r="AK41" s="12"/>
       <c r="AL41" s="12"/>
@@ -13635,7 +13746,7 @@
         <v>263</v>
       </c>
       <c r="L42" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-21</v>
       </c>
       <c r="M42" s="12"/>
@@ -13644,12 +13755,12 @@
         <v>680</v>
       </c>
       <c r="P42" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>48.4</v>
       </c>
       <c r="Q42" s="4"/>
       <c r="R42" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S42" s="16"/>
@@ -13659,7 +13770,7 @@
         <v>23.140495867768596</v>
       </c>
       <c r="V42" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>23.140495867768596</v>
       </c>
       <c r="W42" s="12">
@@ -13697,7 +13808,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI42" s="12"/>
+      <c r="AI42" s="12">
+        <f t="shared" si="7"/>
+        <v>14.52</v>
+      </c>
       <c r="AJ42" s="12"/>
       <c r="AK42" s="12"/>
       <c r="AL42" s="12"/>
@@ -13748,7 +13862,7 @@
         <v>128.352</v>
       </c>
       <c r="L43" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2.9439999999999884</v>
       </c>
       <c r="M43" s="12"/>
@@ -13757,15 +13871,15 @@
         <v>265</v>
       </c>
       <c r="P43" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>26.2592</v>
       </c>
       <c r="Q43" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>139.11999999999998</v>
       </c>
       <c r="R43" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>139</v>
       </c>
       <c r="S43" s="16"/>
@@ -13775,7 +13889,7 @@
         <v>14.995430173044115</v>
       </c>
       <c r="V43" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>9.7020472824762365</v>
       </c>
       <c r="W43" s="12">
@@ -13813,7 +13927,10 @@
         <f t="shared" si="6"/>
         <v>139</v>
       </c>
-      <c r="AI43" s="12"/>
+      <c r="AI43" s="12">
+        <f t="shared" si="7"/>
+        <v>26.2592</v>
+      </c>
       <c r="AJ43" s="12"/>
       <c r="AK43" s="12"/>
       <c r="AL43" s="12"/>
@@ -13864,7 +13981,7 @@
         <v>326.89999999999998</v>
       </c>
       <c r="L44" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4.9900000000000091</v>
       </c>
       <c r="M44" s="12"/>
@@ -13873,15 +13990,15 @@
         <v>474</v>
       </c>
       <c r="P44" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>66.378</v>
       </c>
       <c r="Q44" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>523.41199999999992</v>
       </c>
       <c r="R44" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>523</v>
       </c>
       <c r="S44" s="16"/>
@@ -13891,7 +14008,7 @@
         <v>14.993793124227908</v>
       </c>
       <c r="V44" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>7.1146765494591575</v>
       </c>
       <c r="W44" s="12">
@@ -13929,7 +14046,10 @@
         <f t="shared" si="6"/>
         <v>523</v>
       </c>
-      <c r="AI44" s="12"/>
+      <c r="AI44" s="12">
+        <f t="shared" si="7"/>
+        <v>66.378</v>
+      </c>
       <c r="AJ44" s="12"/>
       <c r="AK44" s="12"/>
       <c r="AL44" s="12"/>
@@ -13980,7 +14100,7 @@
         <v>332</v>
       </c>
       <c r="L45" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-17</v>
       </c>
       <c r="M45" s="12"/>
@@ -13989,15 +14109,15 @@
         <v>868</v>
       </c>
       <c r="P45" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>63</v>
       </c>
       <c r="Q45" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>78</v>
       </c>
       <c r="R45" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>78</v>
       </c>
       <c r="S45" s="16"/>
@@ -14007,7 +14127,7 @@
         <v>15</v>
       </c>
       <c r="V45" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>13.761904761904763</v>
       </c>
       <c r="W45" s="12">
@@ -14045,7 +14165,10 @@
         <f t="shared" si="6"/>
         <v>27.299999999999997</v>
       </c>
-      <c r="AI45" s="12"/>
+      <c r="AI45" s="12">
+        <f t="shared" si="7"/>
+        <v>22.049999999999997</v>
+      </c>
       <c r="AJ45" s="12"/>
       <c r="AK45" s="12"/>
       <c r="AL45" s="12"/>
@@ -14096,7 +14219,7 @@
         <v>325</v>
       </c>
       <c r="L46" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-28</v>
       </c>
       <c r="M46" s="12"/>
@@ -14105,15 +14228,15 @@
         <v>350</v>
       </c>
       <c r="P46" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>59.4</v>
       </c>
       <c r="Q46" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>341</v>
       </c>
       <c r="R46" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>341</v>
       </c>
       <c r="S46" s="16"/>
@@ -14123,7 +14246,7 @@
         <v>15</v>
       </c>
       <c r="V46" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>9.2592592592592595</v>
       </c>
       <c r="W46" s="12">
@@ -14163,7 +14286,10 @@
         <f t="shared" si="6"/>
         <v>139.81</v>
       </c>
-      <c r="AI46" s="12"/>
+      <c r="AI46" s="12">
+        <f t="shared" si="7"/>
+        <v>24.353999999999999</v>
+      </c>
       <c r="AJ46" s="12"/>
       <c r="AK46" s="12"/>
       <c r="AL46" s="12"/>
@@ -14214,7 +14340,7 @@
         <v>181</v>
       </c>
       <c r="L47" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-10</v>
       </c>
       <c r="M47" s="12"/>
@@ -14223,15 +14349,15 @@
         <v>354</v>
       </c>
       <c r="P47" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>34.200000000000003</v>
       </c>
       <c r="Q47" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>105</v>
       </c>
       <c r="R47" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>105</v>
       </c>
       <c r="S47" s="16"/>
@@ -14241,7 +14367,7 @@
         <v>14.999999999999998</v>
       </c>
       <c r="V47" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>11.929824561403509</v>
       </c>
       <c r="W47" s="12">
@@ -14279,7 +14405,10 @@
         <f t="shared" si="6"/>
         <v>43.05</v>
       </c>
-      <c r="AI47" s="12"/>
+      <c r="AI47" s="12">
+        <f t="shared" si="7"/>
+        <v>14.022</v>
+      </c>
       <c r="AJ47" s="12"/>
       <c r="AK47" s="12"/>
       <c r="AL47" s="12"/>
@@ -14330,7 +14459,7 @@
         <v>311</v>
       </c>
       <c r="L48" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-195</v>
       </c>
       <c r="M48" s="12"/>
@@ -14339,12 +14468,12 @@
         <v>600</v>
       </c>
       <c r="P48" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>23.2</v>
       </c>
       <c r="Q48" s="4"/>
       <c r="R48" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S48" s="16"/>
@@ -14354,7 +14483,7 @@
         <v>40.603448275862071</v>
       </c>
       <c r="V48" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>40.603448275862071</v>
       </c>
       <c r="W48" s="12">
@@ -14394,7 +14523,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI48" s="12"/>
+      <c r="AI48" s="12">
+        <f t="shared" si="7"/>
+        <v>8.3520000000000003</v>
+      </c>
       <c r="AJ48" s="12"/>
       <c r="AK48" s="12"/>
       <c r="AL48" s="12"/>
@@ -14443,7 +14575,7 @@
         <v>75</v>
       </c>
       <c r="L49" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-3</v>
       </c>
       <c r="M49" s="12"/>
@@ -14452,7 +14584,7 @@
         <v>73</v>
       </c>
       <c r="P49" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>14.4</v>
       </c>
       <c r="Q49" s="4">
@@ -14460,7 +14592,7 @@
         <v>109.20000000000002</v>
       </c>
       <c r="R49" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>109</v>
       </c>
       <c r="S49" s="16"/>
@@ -14470,7 +14602,7 @@
         <v>12.986111111111111</v>
       </c>
       <c r="V49" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>5.416666666666667</v>
       </c>
       <c r="W49" s="12">
@@ -14508,7 +14640,10 @@
         <f t="shared" si="6"/>
         <v>35.97</v>
       </c>
-      <c r="AI49" s="12"/>
+      <c r="AI49" s="12">
+        <f t="shared" si="7"/>
+        <v>4.7520000000000007</v>
+      </c>
       <c r="AJ49" s="12"/>
       <c r="AK49" s="12"/>
       <c r="AL49" s="12"/>
@@ -14559,7 +14694,7 @@
         <v>124</v>
       </c>
       <c r="L50" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-2</v>
       </c>
       <c r="M50" s="12"/>
@@ -14568,7 +14703,7 @@
         <v>132</v>
       </c>
       <c r="P50" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>24.4</v>
       </c>
       <c r="Q50" s="4">
@@ -14576,7 +14711,7 @@
         <v>186.2</v>
       </c>
       <c r="R50" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>186</v>
       </c>
       <c r="S50" s="16"/>
@@ -14586,7 +14721,7 @@
         <v>12.991803278688526</v>
       </c>
       <c r="V50" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>5.3688524590163942</v>
       </c>
       <c r="W50" s="12">
@@ -14624,7 +14759,10 @@
         <f t="shared" si="6"/>
         <v>74.400000000000006</v>
       </c>
-      <c r="AI50" s="12"/>
+      <c r="AI50" s="12">
+        <f t="shared" si="7"/>
+        <v>9.76</v>
+      </c>
       <c r="AJ50" s="12"/>
       <c r="AK50" s="12"/>
       <c r="AL50" s="12"/>
@@ -14673,7 +14811,7 @@
         <v>30</v>
       </c>
       <c r="L51" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-2</v>
       </c>
       <c r="M51" s="12"/>
@@ -14682,15 +14820,15 @@
         <v>66</v>
       </c>
       <c r="P51" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5.6</v>
       </c>
       <c r="Q51" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>18</v>
       </c>
       <c r="R51" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>18</v>
       </c>
       <c r="S51" s="16"/>
@@ -14700,7 +14838,7 @@
         <v>15.000000000000002</v>
       </c>
       <c r="V51" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>11.785714285714286</v>
       </c>
       <c r="W51" s="12">
@@ -14738,7 +14876,10 @@
         <f t="shared" si="6"/>
         <v>5.94</v>
       </c>
-      <c r="AI51" s="12"/>
+      <c r="AI51" s="12">
+        <f t="shared" si="7"/>
+        <v>1.8479999999999999</v>
+      </c>
       <c r="AJ51" s="12"/>
       <c r="AK51" s="12"/>
       <c r="AL51" s="12"/>
@@ -14787,7 +14928,7 @@
         <v>369.3</v>
       </c>
       <c r="L52" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>27.50200000000001</v>
       </c>
       <c r="M52" s="12"/>
@@ -14796,15 +14937,15 @@
         <v>721</v>
       </c>
       <c r="P52" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>79.360399999999998</v>
       </c>
       <c r="Q52" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>408.14099999999996</v>
       </c>
       <c r="R52" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>408</v>
       </c>
       <c r="S52" s="16"/>
@@ -14814,7 +14955,7 @@
         <v>14.998223295245486</v>
       </c>
       <c r="V52" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>9.8571201758055658</v>
       </c>
       <c r="W52" s="12">
@@ -14852,7 +14993,10 @@
         <f t="shared" si="6"/>
         <v>408</v>
       </c>
-      <c r="AI52" s="12"/>
+      <c r="AI52" s="12">
+        <f t="shared" si="7"/>
+        <v>79.360399999999998</v>
+      </c>
       <c r="AJ52" s="12"/>
       <c r="AK52" s="12"/>
       <c r="AL52" s="12"/>
@@ -14903,7 +15047,7 @@
         <v>83</v>
       </c>
       <c r="L53" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-15</v>
       </c>
       <c r="M53" s="12"/>
@@ -14912,12 +15056,12 @@
         <v>241</v>
       </c>
       <c r="P53" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>13.6</v>
       </c>
       <c r="Q53" s="4"/>
       <c r="R53" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S53" s="16"/>
@@ -14927,7 +15071,7 @@
         <v>22.352941176470591</v>
       </c>
       <c r="V53" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>22.352941176470591</v>
       </c>
       <c r="W53" s="12">
@@ -14965,7 +15109,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI53" s="12"/>
+      <c r="AI53" s="12">
+        <f t="shared" si="7"/>
+        <v>5.44</v>
+      </c>
       <c r="AJ53" s="12"/>
       <c r="AK53" s="12"/>
       <c r="AL53" s="12"/>
@@ -15016,7 +15163,7 @@
         <v>23.9</v>
       </c>
       <c r="L54" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2.84</v>
       </c>
       <c r="M54" s="12"/>
@@ -15025,7 +15172,7 @@
         <v>0</v>
       </c>
       <c r="P54" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5.3479999999999999</v>
       </c>
       <c r="Q54" s="4">
@@ -15033,7 +15180,7 @@
         <v>45.29</v>
       </c>
       <c r="R54" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>45</v>
       </c>
       <c r="S54" s="16"/>
@@ -15043,7 +15190,7 @@
         <v>13.94577412116679</v>
       </c>
       <c r="V54" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>5.5314136125654452</v>
       </c>
       <c r="W54" s="12">
@@ -15083,7 +15230,10 @@
         <f t="shared" si="6"/>
         <v>45</v>
       </c>
-      <c r="AI54" s="12"/>
+      <c r="AI54" s="12">
+        <f t="shared" si="7"/>
+        <v>5.3479999999999999</v>
+      </c>
       <c r="AJ54" s="12"/>
       <c r="AK54" s="12"/>
       <c r="AL54" s="12"/>
@@ -15132,7 +15282,7 @@
         <v>25.1</v>
       </c>
       <c r="L55" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-4.1450000000000031</v>
       </c>
       <c r="M55" s="12"/>
@@ -15141,12 +15291,12 @@
         <v>70</v>
       </c>
       <c r="P55" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4.1909999999999998</v>
       </c>
       <c r="Q55" s="4"/>
       <c r="R55" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S55" s="16"/>
@@ -15156,7 +15306,7 @@
         <v>22.059174421379147</v>
       </c>
       <c r="V55" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>22.059174421379147</v>
       </c>
       <c r="W55" s="12">
@@ -15194,7 +15344,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI55" s="12"/>
+      <c r="AI55" s="12">
+        <f t="shared" si="7"/>
+        <v>4.1909999999999998</v>
+      </c>
       <c r="AJ55" s="12"/>
       <c r="AK55" s="12"/>
       <c r="AL55" s="12"/>
@@ -15233,7 +15386,7 @@
       <c r="J56" s="8"/>
       <c r="K56" s="8"/>
       <c r="L56" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="M56" s="8"/>
@@ -15242,12 +15395,12 @@
         <v>0</v>
       </c>
       <c r="P56" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Q56" s="10"/>
       <c r="R56" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S56" s="16"/>
@@ -15257,7 +15410,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="V56" s="8" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W56" s="8">
@@ -15297,7 +15450,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI56" s="12"/>
+      <c r="AI56" s="12">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AJ56" s="12"/>
       <c r="AK56" s="12"/>
       <c r="AL56" s="12"/>
@@ -15344,7 +15500,7 @@
         <v>13.78</v>
       </c>
       <c r="L57" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-13.78</v>
       </c>
       <c r="M57" s="8"/>
@@ -15353,12 +15509,12 @@
         <v>0</v>
       </c>
       <c r="P57" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Q57" s="10"/>
       <c r="R57" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S57" s="16"/>
@@ -15368,7 +15524,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="V57" s="8" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W57" s="8">
@@ -15406,7 +15562,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI57" s="12"/>
+      <c r="AI57" s="12">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AJ57" s="12"/>
       <c r="AK57" s="12"/>
       <c r="AL57" s="12"/>
@@ -15455,7 +15614,7 @@
         <v>35</v>
       </c>
       <c r="L58" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-1</v>
       </c>
       <c r="M58" s="12"/>
@@ -15464,15 +15623,15 @@
         <v>19</v>
       </c>
       <c r="P58" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>6.8</v>
       </c>
       <c r="Q58" s="4">
-        <f t="shared" ref="Q58:Q62" si="15">15*P58-O58-F58</f>
+        <f t="shared" ref="Q58:Q62" si="16">15*P58-O58-F58</f>
         <v>29</v>
       </c>
       <c r="R58" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>29</v>
       </c>
       <c r="S58" s="16"/>
@@ -15482,7 +15641,7 @@
         <v>15</v>
       </c>
       <c r="V58" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>10.73529411764706</v>
       </c>
       <c r="W58" s="12">
@@ -15522,7 +15681,10 @@
         <f t="shared" si="6"/>
         <v>7.25</v>
       </c>
-      <c r="AI58" s="12"/>
+      <c r="AI58" s="12">
+        <f t="shared" si="7"/>
+        <v>1.7</v>
+      </c>
       <c r="AJ58" s="12"/>
       <c r="AK58" s="12"/>
       <c r="AL58" s="12"/>
@@ -15573,7 +15735,7 @@
         <v>53.1</v>
       </c>
       <c r="L59" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-9.8530000000000015</v>
       </c>
       <c r="M59" s="12"/>
@@ -15582,15 +15744,15 @@
         <v>54</v>
       </c>
       <c r="P59" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>8.6494</v>
       </c>
       <c r="Q59" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>34.493999999999986</v>
       </c>
       <c r="R59" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>34</v>
       </c>
       <c r="S59" s="16"/>
@@ -15600,7 +15762,7 @@
         <v>14.942886211760355</v>
       </c>
       <c r="V59" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>11.011977709436493</v>
       </c>
       <c r="W59" s="12">
@@ -15638,7 +15800,10 @@
         <f t="shared" si="6"/>
         <v>34</v>
       </c>
-      <c r="AI59" s="12"/>
+      <c r="AI59" s="12">
+        <f t="shared" si="7"/>
+        <v>8.6494</v>
+      </c>
       <c r="AJ59" s="12"/>
       <c r="AK59" s="12"/>
       <c r="AL59" s="12"/>
@@ -15685,7 +15850,7 @@
         <v>178</v>
       </c>
       <c r="L60" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-91</v>
       </c>
       <c r="M60" s="12"/>
@@ -15694,15 +15859,15 @@
         <v>180</v>
       </c>
       <c r="P60" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>17.399999999999999</v>
       </c>
       <c r="Q60" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>80</v>
       </c>
       <c r="R60" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>80</v>
       </c>
       <c r="S60" s="16"/>
@@ -15712,7 +15877,7 @@
         <v>15.000000000000002</v>
       </c>
       <c r="V60" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>10.402298850574713</v>
       </c>
       <c r="W60" s="12">
@@ -15752,7 +15917,10 @@
         <f t="shared" si="6"/>
         <v>21.6</v>
       </c>
-      <c r="AI60" s="12"/>
+      <c r="AI60" s="12">
+        <f t="shared" si="7"/>
+        <v>4.6979999999999995</v>
+      </c>
       <c r="AJ60" s="12"/>
       <c r="AK60" s="12"/>
       <c r="AL60" s="12"/>
@@ -15799,7 +15967,7 @@
         <v>161</v>
       </c>
       <c r="L61" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-84</v>
       </c>
       <c r="M61" s="12"/>
@@ -15808,7 +15976,7 @@
         <v>300</v>
       </c>
       <c r="P61" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>15.4</v>
       </c>
       <c r="Q61" s="4"/>
@@ -15829,7 +15997,7 @@
         <v>38.961038961038959</v>
       </c>
       <c r="V61" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>19.480519480519479</v>
       </c>
       <c r="W61" s="12">
@@ -15869,7 +16037,10 @@
         <f t="shared" si="6"/>
         <v>90</v>
       </c>
-      <c r="AI61" s="12"/>
+      <c r="AI61" s="12">
+        <f t="shared" si="7"/>
+        <v>4.62</v>
+      </c>
       <c r="AJ61" s="12"/>
       <c r="AK61" s="12"/>
       <c r="AL61" s="12"/>
@@ -15921,7 +16092,7 @@
         <v>600</v>
       </c>
       <c r="L62" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-12</v>
       </c>
       <c r="M62" s="12"/>
@@ -15930,15 +16101,15 @@
         <v>700</v>
       </c>
       <c r="P62" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>117.6</v>
       </c>
       <c r="Q62" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>616</v>
       </c>
       <c r="R62" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>616</v>
       </c>
       <c r="S62" s="16"/>
@@ -15948,7 +16119,7 @@
         <v>15</v>
       </c>
       <c r="V62" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>9.7619047619047628</v>
       </c>
       <c r="W62" s="12">
@@ -15988,7 +16159,10 @@
         <f t="shared" si="6"/>
         <v>252.55999999999997</v>
       </c>
-      <c r="AI62" s="12"/>
+      <c r="AI62" s="12">
+        <f t="shared" si="7"/>
+        <v>48.215999999999994</v>
+      </c>
       <c r="AJ62" s="12"/>
       <c r="AK62" s="12"/>
       <c r="AL62" s="12"/>
@@ -16035,7 +16209,7 @@
         <v>2</v>
       </c>
       <c r="L63" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-2</v>
       </c>
       <c r="M63" s="8"/>
@@ -16044,12 +16218,12 @@
         <v>0</v>
       </c>
       <c r="P63" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S63" s="16"/>
@@ -16059,7 +16233,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="V63" s="8" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W63" s="8">
@@ -16099,7 +16273,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI63" s="12"/>
+      <c r="AI63" s="12">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AJ63" s="12"/>
       <c r="AK63" s="12"/>
       <c r="AL63" s="12"/>
@@ -16150,7 +16327,7 @@
         <v>604.5</v>
       </c>
       <c r="L64" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>12.100000000000023</v>
       </c>
       <c r="M64" s="12"/>
@@ -16159,15 +16336,15 @@
         <v>501</v>
       </c>
       <c r="P64" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>123.32000000000001</v>
       </c>
       <c r="Q64" s="4">
-        <f t="shared" ref="Q64:Q82" si="16">15*P64-O64-F64</f>
+        <f t="shared" ref="Q64:Q82" si="17">15*P64-O64-F64</f>
         <v>552.92400000000021</v>
       </c>
       <c r="R64" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>553</v>
       </c>
       <c r="S64" s="16"/>
@@ -16177,7 +16354,7 @@
         <v>15.000616282841387</v>
       </c>
       <c r="V64" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>10.516347713266299</v>
       </c>
       <c r="W64" s="12">
@@ -16215,7 +16392,10 @@
         <f t="shared" si="6"/>
         <v>553</v>
       </c>
-      <c r="AI64" s="12"/>
+      <c r="AI64" s="12">
+        <f t="shared" si="7"/>
+        <v>123.32000000000001</v>
+      </c>
       <c r="AJ64" s="12"/>
       <c r="AK64" s="12"/>
       <c r="AL64" s="12"/>
@@ -16266,7 +16446,7 @@
         <v>46</v>
       </c>
       <c r="L65" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="M65" s="12"/>
@@ -16275,7 +16455,7 @@
         <v>40</v>
       </c>
       <c r="P65" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>9.1999999999999993</v>
       </c>
       <c r="Q65" s="4">
@@ -16283,7 +16463,7 @@
         <v>76.799999999999983</v>
       </c>
       <c r="R65" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>77</v>
       </c>
       <c r="S65" s="16"/>
@@ -16293,7 +16473,7 @@
         <v>14.021739130434783</v>
       </c>
       <c r="V65" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>5.6521739130434785</v>
       </c>
       <c r="W65" s="12">
@@ -16331,7 +16511,10 @@
         <f t="shared" si="6"/>
         <v>26.95</v>
       </c>
-      <c r="AI65" s="12"/>
+      <c r="AI65" s="12">
+        <f t="shared" si="7"/>
+        <v>3.2199999999999998</v>
+      </c>
       <c r="AJ65" s="12"/>
       <c r="AK65" s="12"/>
       <c r="AL65" s="12"/>
@@ -16382,7 +16565,7 @@
         <v>63.5</v>
       </c>
       <c r="L66" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>3.2740000000000009</v>
       </c>
       <c r="M66" s="12"/>
@@ -16391,15 +16574,15 @@
         <v>70</v>
       </c>
       <c r="P66" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>13.354800000000001</v>
       </c>
       <c r="Q66" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>68.299000000000007</v>
       </c>
       <c r="R66" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>68</v>
       </c>
       <c r="S66" s="16"/>
@@ -16409,7 +16592,7 @@
         <v>14.977611046215591</v>
       </c>
       <c r="V66" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>9.8858088477551131</v>
       </c>
       <c r="W66" s="12">
@@ -16447,7 +16630,10 @@
         <f t="shared" si="6"/>
         <v>68</v>
       </c>
-      <c r="AI66" s="12"/>
+      <c r="AI66" s="12">
+        <f t="shared" si="7"/>
+        <v>13.354800000000001</v>
+      </c>
       <c r="AJ66" s="12"/>
       <c r="AK66" s="12"/>
       <c r="AL66" s="12"/>
@@ -16498,7 +16684,7 @@
         <v>359</v>
       </c>
       <c r="L67" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-2</v>
       </c>
       <c r="M67" s="12"/>
@@ -16507,15 +16693,15 @@
         <v>200</v>
       </c>
       <c r="P67" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>71.400000000000006</v>
       </c>
       <c r="Q67" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>352</v>
       </c>
       <c r="R67" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>352</v>
       </c>
       <c r="S67" s="16"/>
@@ -16525,7 +16711,7 @@
         <v>14.999999999999998</v>
       </c>
       <c r="V67" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>10.070028011204482</v>
       </c>
       <c r="W67" s="12">
@@ -16565,7 +16751,10 @@
         <f t="shared" si="6"/>
         <v>144.32</v>
       </c>
-      <c r="AI67" s="12"/>
+      <c r="AI67" s="12">
+        <f t="shared" si="7"/>
+        <v>29.274000000000001</v>
+      </c>
       <c r="AJ67" s="12"/>
       <c r="AK67" s="12"/>
       <c r="AL67" s="12"/>
@@ -16614,7 +16803,7 @@
         <v>177</v>
       </c>
       <c r="L68" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>9.3489999999999895</v>
       </c>
       <c r="M68" s="12"/>
@@ -16623,15 +16812,15 @@
         <v>335</v>
       </c>
       <c r="P68" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>37.269799999999996</v>
       </c>
       <c r="Q68" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>45.973999999999904</v>
       </c>
       <c r="R68" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>46</v>
       </c>
       <c r="S68" s="16"/>
@@ -16641,7 +16830,7 @@
         <v>15.00069761576397</v>
       </c>
       <c r="V68" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>13.766454341048249</v>
       </c>
       <c r="W68" s="12">
@@ -16679,7 +16868,10 @@
         <f t="shared" si="6"/>
         <v>46</v>
       </c>
-      <c r="AI68" s="12"/>
+      <c r="AI68" s="12">
+        <f t="shared" si="7"/>
+        <v>37.269799999999996</v>
+      </c>
       <c r="AJ68" s="12"/>
       <c r="AK68" s="12"/>
       <c r="AL68" s="12"/>
@@ -16726,7 +16918,7 @@
         <v>97</v>
       </c>
       <c r="L69" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-19</v>
       </c>
       <c r="M69" s="12"/>
@@ -16735,15 +16927,15 @@
         <v>168</v>
       </c>
       <c r="P69" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>15.6</v>
       </c>
       <c r="Q69" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>66</v>
       </c>
       <c r="R69" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>66</v>
       </c>
       <c r="S69" s="16"/>
@@ -16753,7 +16945,7 @@
         <v>15</v>
       </c>
       <c r="V69" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>10.76923076923077</v>
       </c>
       <c r="W69" s="12">
@@ -16791,7 +16983,10 @@
         <f t="shared" si="6"/>
         <v>19.8</v>
       </c>
-      <c r="AI69" s="12"/>
+      <c r="AI69" s="12">
+        <f t="shared" si="7"/>
+        <v>4.68</v>
+      </c>
       <c r="AJ69" s="12"/>
       <c r="AK69" s="12"/>
       <c r="AL69" s="12"/>
@@ -16842,7 +17037,7 @@
         <v>261</v>
       </c>
       <c r="L70" s="12">
-        <f t="shared" ref="L70:L101" si="17">E70-K70</f>
+        <f t="shared" ref="L70:L101" si="18">E70-K70</f>
         <v>-18</v>
       </c>
       <c r="M70" s="12"/>
@@ -16851,12 +17046,12 @@
         <v>316</v>
       </c>
       <c r="P70" s="12">
-        <f t="shared" ref="P70:P105" si="18">E70/5</f>
+        <f t="shared" ref="P70:P105" si="19">E70/5</f>
         <v>48.6</v>
       </c>
       <c r="Q70" s="4"/>
       <c r="R70" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S70" s="16"/>
@@ -16866,7 +17061,7 @@
         <v>15.596707818930041</v>
       </c>
       <c r="V70" s="12">
-        <f t="shared" ref="V70:V105" si="19">(F70+O70)/P70</f>
+        <f t="shared" ref="V70:V105" si="20">(F70+O70)/P70</f>
         <v>15.596707818930041</v>
       </c>
       <c r="W70" s="12">
@@ -16904,7 +17099,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI70" s="12"/>
+      <c r="AI70" s="12">
+        <f t="shared" si="7"/>
+        <v>8.7479999999999993</v>
+      </c>
       <c r="AJ70" s="12"/>
       <c r="AK70" s="12"/>
       <c r="AL70" s="12"/>
@@ -16953,7 +17151,7 @@
         <v>73</v>
       </c>
       <c r="L71" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-2</v>
       </c>
       <c r="M71" s="12"/>
@@ -16962,7 +17160,7 @@
         <v>0</v>
       </c>
       <c r="P71" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>14.2</v>
       </c>
       <c r="Q71" s="4">
@@ -16982,11 +17180,11 @@
         <v xml:space="preserve">нет потребности </v>
       </c>
       <c r="U71" s="12">
-        <f t="shared" ref="U71:U105" si="20">(F71+O71+R71)/P71</f>
+        <f t="shared" ref="U71:U105" si="21">(F71+O71+R71)/P71</f>
         <v>6.971830985915493</v>
       </c>
       <c r="V71" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>3.450704225352113</v>
       </c>
       <c r="W71" s="12">
@@ -17021,10 +17219,13 @@
       </c>
       <c r="AG71" s="12"/>
       <c r="AH71" s="12">
-        <f t="shared" ref="AH71:AH105" si="21">G71*R71</f>
+        <f t="shared" ref="AH71:AH105" si="22">G71*R71</f>
         <v>42</v>
       </c>
-      <c r="AI71" s="12"/>
+      <c r="AI71" s="12">
+        <f t="shared" ref="AI71:AI105" si="23">P71*G71</f>
+        <v>11.927999999999999</v>
+      </c>
       <c r="AJ71" s="12"/>
       <c r="AK71" s="12"/>
       <c r="AL71" s="12"/>
@@ -17075,7 +17276,7 @@
         <v>460</v>
       </c>
       <c r="L72" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-7</v>
       </c>
       <c r="M72" s="12"/>
@@ -17084,25 +17285,25 @@
         <v>943</v>
       </c>
       <c r="P72" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>90.6</v>
       </c>
       <c r="Q72" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>160</v>
       </c>
       <c r="R72" s="4">
-        <f t="shared" ref="R71:R105" si="22">ROUND(Q72,0)</f>
+        <f t="shared" ref="R72:R105" si="24">ROUND(Q72,0)</f>
         <v>160</v>
       </c>
       <c r="S72" s="16"/>
       <c r="T72" s="16"/>
       <c r="U72" s="12">
+        <f t="shared" si="21"/>
+        <v>15.000000000000002</v>
+      </c>
+      <c r="V72" s="12">
         <f t="shared" si="20"/>
-        <v>15.000000000000002</v>
-      </c>
-      <c r="V72" s="12">
-        <f t="shared" si="19"/>
         <v>13.233995584988964</v>
       </c>
       <c r="W72" s="12">
@@ -17137,10 +17338,13 @@
       </c>
       <c r="AG72" s="12"/>
       <c r="AH72" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>56</v>
       </c>
-      <c r="AI72" s="12"/>
+      <c r="AI72" s="12">
+        <f t="shared" si="23"/>
+        <v>31.709999999999997</v>
+      </c>
       <c r="AJ72" s="12"/>
       <c r="AK72" s="12"/>
       <c r="AL72" s="12"/>
@@ -17179,7 +17383,7 @@
       <c r="J73" s="12"/>
       <c r="K73" s="12"/>
       <c r="L73" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M73" s="12"/>
@@ -17188,7 +17392,7 @@
         <v>300</v>
       </c>
       <c r="P73" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Q73" s="4"/>
@@ -17205,13 +17409,13 @@
         <v xml:space="preserve">Для розница </v>
       </c>
       <c r="U73" s="12" t="e">
+        <f t="shared" si="21"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V73" s="12" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V73" s="12" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
       <c r="W73" s="12">
         <v>0</v>
       </c>
@@ -17246,10 +17450,13 @@
         <v>123</v>
       </c>
       <c r="AH73" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>35</v>
       </c>
-      <c r="AI73" s="12"/>
+      <c r="AI73" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="AJ73" s="12"/>
       <c r="AK73" s="12"/>
       <c r="AL73" s="12"/>
@@ -17298,7 +17505,7 @@
         <v>168.7</v>
       </c>
       <c r="L74" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>7.2470000000000141</v>
       </c>
       <c r="M74" s="12"/>
@@ -17307,24 +17514,24 @@
         <v>604</v>
       </c>
       <c r="P74" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>35.189399999999999</v>
       </c>
       <c r="Q74" s="4"/>
       <c r="R74" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="S74" s="16"/>
       <c r="T74" s="16"/>
       <c r="U74" s="12">
+        <f t="shared" si="21"/>
+        <v>19.371600538798614</v>
+      </c>
+      <c r="V74" s="12">
         <f t="shared" si="20"/>
         <v>19.371600538798614</v>
       </c>
-      <c r="V74" s="12">
-        <f t="shared" si="19"/>
-        <v>19.371600538798614</v>
-      </c>
       <c r="W74" s="12">
         <v>67.367999999999995</v>
       </c>
@@ -17357,10 +17564,13 @@
       </c>
       <c r="AG74" s="12"/>
       <c r="AH74" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AI74" s="12"/>
+      <c r="AI74" s="12">
+        <f t="shared" si="23"/>
+        <v>35.189399999999999</v>
+      </c>
       <c r="AJ74" s="12"/>
       <c r="AK74" s="12"/>
       <c r="AL74" s="12"/>
@@ -17409,7 +17619,7 @@
         <v>263</v>
       </c>
       <c r="L75" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>18.120999999999981</v>
       </c>
       <c r="M75" s="12"/>
@@ -17418,25 +17628,25 @@
         <v>704</v>
       </c>
       <c r="P75" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>56.224199999999996</v>
       </c>
       <c r="Q75" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>111.57399999999994</v>
       </c>
       <c r="R75" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>112</v>
       </c>
       <c r="S75" s="16"/>
       <c r="T75" s="16"/>
       <c r="U75" s="12">
+        <f t="shared" si="21"/>
+        <v>15.007576808562861</v>
+      </c>
+      <c r="V75" s="12">
         <f t="shared" si="20"/>
-        <v>15.007576808562861</v>
-      </c>
-      <c r="V75" s="12">
-        <f t="shared" si="19"/>
         <v>13.015552022083018</v>
       </c>
       <c r="W75" s="12">
@@ -17471,10 +17681,13 @@
       </c>
       <c r="AG75" s="12"/>
       <c r="AH75" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>112</v>
       </c>
-      <c r="AI75" s="12"/>
+      <c r="AI75" s="12">
+        <f t="shared" si="23"/>
+        <v>56.224199999999996</v>
+      </c>
       <c r="AJ75" s="12"/>
       <c r="AK75" s="12"/>
       <c r="AL75" s="12"/>
@@ -17523,7 +17736,7 @@
         <v>219</v>
       </c>
       <c r="L76" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-10</v>
       </c>
       <c r="M76" s="12"/>
@@ -17532,25 +17745,25 @@
         <v>569</v>
       </c>
       <c r="P76" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>41.8</v>
       </c>
       <c r="Q76" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>21</v>
       </c>
       <c r="R76" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>21</v>
       </c>
       <c r="S76" s="16"/>
       <c r="T76" s="16"/>
       <c r="U76" s="12">
+        <f t="shared" si="21"/>
+        <v>15.000000000000002</v>
+      </c>
+      <c r="V76" s="12">
         <f t="shared" si="20"/>
-        <v>15.000000000000002</v>
-      </c>
-      <c r="V76" s="12">
-        <f t="shared" si="19"/>
         <v>14.497607655502394</v>
       </c>
       <c r="W76" s="12">
@@ -17585,10 +17798,13 @@
       </c>
       <c r="AG76" s="12"/>
       <c r="AH76" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>7.35</v>
       </c>
-      <c r="AI76" s="12"/>
+      <c r="AI76" s="12">
+        <f t="shared" si="23"/>
+        <v>14.629999999999997</v>
+      </c>
       <c r="AJ76" s="12"/>
       <c r="AK76" s="12"/>
       <c r="AL76" s="12"/>
@@ -17639,7 +17855,7 @@
         <v>70</v>
       </c>
       <c r="L77" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-4</v>
       </c>
       <c r="M77" s="12"/>
@@ -17648,25 +17864,25 @@
         <v>90</v>
       </c>
       <c r="P77" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>13.2</v>
       </c>
       <c r="Q77" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>71</v>
       </c>
       <c r="R77" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>71</v>
       </c>
       <c r="S77" s="16"/>
       <c r="T77" s="16"/>
       <c r="U77" s="12">
+        <f t="shared" si="21"/>
+        <v>15</v>
+      </c>
+      <c r="V77" s="12">
         <f t="shared" si="20"/>
-        <v>15</v>
-      </c>
-      <c r="V77" s="12">
-        <f t="shared" si="19"/>
         <v>9.6212121212121211</v>
       </c>
       <c r="W77" s="12">
@@ -17701,10 +17917,13 @@
       </c>
       <c r="AG77" s="12"/>
       <c r="AH77" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>21.3</v>
       </c>
-      <c r="AI77" s="12"/>
+      <c r="AI77" s="12">
+        <f t="shared" si="23"/>
+        <v>3.9599999999999995</v>
+      </c>
       <c r="AJ77" s="12"/>
       <c r="AK77" s="12"/>
       <c r="AL77" s="12"/>
@@ -17755,7 +17974,7 @@
         <v>81</v>
       </c>
       <c r="L78" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M78" s="12"/>
@@ -17764,25 +17983,25 @@
         <v>116</v>
       </c>
       <c r="P78" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>16.2</v>
       </c>
       <c r="Q78" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>66</v>
       </c>
       <c r="R78" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>66</v>
       </c>
       <c r="S78" s="16"/>
       <c r="T78" s="16"/>
       <c r="U78" s="12">
+        <f t="shared" si="21"/>
+        <v>15</v>
+      </c>
+      <c r="V78" s="12">
         <f t="shared" si="20"/>
-        <v>15</v>
-      </c>
-      <c r="V78" s="12">
-        <f t="shared" si="19"/>
         <v>10.925925925925926</v>
       </c>
       <c r="W78" s="12">
@@ -17817,10 +18036,13 @@
       </c>
       <c r="AG78" s="12"/>
       <c r="AH78" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>19.8</v>
       </c>
-      <c r="AI78" s="12"/>
+      <c r="AI78" s="12">
+        <f t="shared" si="23"/>
+        <v>4.8599999999999994</v>
+      </c>
       <c r="AJ78" s="12"/>
       <c r="AK78" s="12"/>
       <c r="AL78" s="12"/>
@@ -17871,7 +18093,7 @@
         <v>146</v>
       </c>
       <c r="L79" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-7</v>
       </c>
       <c r="M79" s="12"/>
@@ -17880,25 +18102,25 @@
         <v>144</v>
       </c>
       <c r="P79" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>27.8</v>
       </c>
       <c r="Q79" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>113</v>
       </c>
       <c r="R79" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>113</v>
       </c>
       <c r="S79" s="16"/>
       <c r="T79" s="16"/>
       <c r="U79" s="12">
+        <f t="shared" si="21"/>
+        <v>15</v>
+      </c>
+      <c r="V79" s="12">
         <f t="shared" si="20"/>
-        <v>15</v>
-      </c>
-      <c r="V79" s="12">
-        <f t="shared" si="19"/>
         <v>10.935251798561151</v>
       </c>
       <c r="W79" s="12">
@@ -17933,10 +18155,13 @@
       </c>
       <c r="AG79" s="12"/>
       <c r="AH79" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>31.640000000000004</v>
       </c>
-      <c r="AI79" s="12"/>
+      <c r="AI79" s="12">
+        <f t="shared" si="23"/>
+        <v>7.7840000000000007</v>
+      </c>
       <c r="AJ79" s="12"/>
       <c r="AK79" s="12"/>
       <c r="AL79" s="12"/>
@@ -17987,7 +18212,7 @@
         <v>173</v>
       </c>
       <c r="L80" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-6</v>
       </c>
       <c r="M80" s="12"/>
@@ -17996,25 +18221,25 @@
         <v>376</v>
       </c>
       <c r="P80" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>33.4</v>
       </c>
       <c r="Q80" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>57</v>
       </c>
       <c r="R80" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>57</v>
       </c>
       <c r="S80" s="16"/>
       <c r="T80" s="16"/>
       <c r="U80" s="12">
+        <f t="shared" si="21"/>
+        <v>15</v>
+      </c>
+      <c r="V80" s="12">
         <f t="shared" si="20"/>
-        <v>15</v>
-      </c>
-      <c r="V80" s="12">
-        <f t="shared" si="19"/>
         <v>13.293413173652695</v>
       </c>
       <c r="W80" s="12">
@@ -18049,10 +18274,13 @@
       </c>
       <c r="AG80" s="12"/>
       <c r="AH80" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>15.96</v>
       </c>
-      <c r="AI80" s="12"/>
+      <c r="AI80" s="12">
+        <f t="shared" si="23"/>
+        <v>9.3520000000000003</v>
+      </c>
       <c r="AJ80" s="12"/>
       <c r="AK80" s="12"/>
       <c r="AL80" s="12"/>
@@ -18103,7 +18331,7 @@
         <v>491</v>
       </c>
       <c r="L81" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-5</v>
       </c>
       <c r="M81" s="12"/>
@@ -18112,25 +18340,25 @@
         <v>509</v>
       </c>
       <c r="P81" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>97.2</v>
       </c>
       <c r="Q81" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>493</v>
       </c>
       <c r="R81" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>493</v>
       </c>
       <c r="S81" s="16"/>
       <c r="T81" s="16"/>
       <c r="U81" s="12">
+        <f t="shared" si="21"/>
+        <v>15</v>
+      </c>
+      <c r="V81" s="12">
         <f t="shared" si="20"/>
-        <v>15</v>
-      </c>
-      <c r="V81" s="12">
-        <f t="shared" si="19"/>
         <v>9.9279835390946491</v>
       </c>
       <c r="W81" s="12">
@@ -18165,10 +18393,13 @@
       </c>
       <c r="AG81" s="12"/>
       <c r="AH81" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>138.04000000000002</v>
       </c>
-      <c r="AI81" s="12"/>
+      <c r="AI81" s="12">
+        <f t="shared" si="23"/>
+        <v>27.216000000000005</v>
+      </c>
       <c r="AJ81" s="12"/>
       <c r="AK81" s="12"/>
       <c r="AL81" s="12"/>
@@ -18219,7 +18450,7 @@
         <v>208</v>
       </c>
       <c r="L82" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-7</v>
       </c>
       <c r="M82" s="12"/>
@@ -18228,25 +18459,25 @@
         <v>229</v>
       </c>
       <c r="P82" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>40.200000000000003</v>
       </c>
       <c r="Q82" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>207</v>
       </c>
       <c r="R82" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>207</v>
       </c>
       <c r="S82" s="16"/>
       <c r="T82" s="16"/>
       <c r="U82" s="12">
+        <f t="shared" si="21"/>
+        <v>14.999999999999998</v>
+      </c>
+      <c r="V82" s="12">
         <f t="shared" si="20"/>
-        <v>14.999999999999998</v>
-      </c>
-      <c r="V82" s="12">
-        <f t="shared" si="19"/>
         <v>9.8507462686567155</v>
       </c>
       <c r="W82" s="12">
@@ -18281,10 +18512,13 @@
       </c>
       <c r="AG82" s="12"/>
       <c r="AH82" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>82.800000000000011</v>
       </c>
-      <c r="AI82" s="12"/>
+      <c r="AI82" s="12">
+        <f t="shared" si="23"/>
+        <v>16.080000000000002</v>
+      </c>
       <c r="AJ82" s="12"/>
       <c r="AK82" s="12"/>
       <c r="AL82" s="12"/>
@@ -18331,7 +18565,7 @@
       </c>
       <c r="K83" s="8"/>
       <c r="L83" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M83" s="8"/>
@@ -18340,24 +18574,24 @@
         <v>0</v>
       </c>
       <c r="P83" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="S83" s="16"/>
       <c r="T83" s="16"/>
       <c r="U83" s="12" t="e">
+        <f t="shared" si="21"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V83" s="8" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V83" s="8" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
       <c r="W83" s="8">
         <v>0.6</v>
       </c>
@@ -18392,10 +18626,13 @@
         <v>135</v>
       </c>
       <c r="AH83" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AI83" s="12"/>
+      <c r="AI83" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="AJ83" s="12"/>
       <c r="AK83" s="12"/>
       <c r="AL83" s="12"/>
@@ -18446,7 +18683,7 @@
         <v>90.795000000000002</v>
       </c>
       <c r="L84" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-31.066000000000003</v>
       </c>
       <c r="M84" s="12"/>
@@ -18455,7 +18692,7 @@
         <v>128</v>
       </c>
       <c r="P84" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>11.9458</v>
       </c>
       <c r="Q84" s="4">
@@ -18474,11 +18711,11 @@
         <v>Задача для ТП</v>
       </c>
       <c r="U84" s="12">
+        <f t="shared" si="21"/>
+        <v>19.989117514105377</v>
+      </c>
+      <c r="V84" s="12">
         <f t="shared" si="20"/>
-        <v>19.989117514105377</v>
-      </c>
-      <c r="V84" s="12">
-        <f t="shared" si="19"/>
         <v>10.780860218654254</v>
       </c>
       <c r="W84" s="12">
@@ -18515,10 +18752,13 @@
         <v>107</v>
       </c>
       <c r="AH84" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>110</v>
       </c>
-      <c r="AI84" s="12"/>
+      <c r="AI84" s="12">
+        <f t="shared" si="23"/>
+        <v>11.9458</v>
+      </c>
       <c r="AJ84" s="12"/>
       <c r="AK84" s="12"/>
       <c r="AL84" s="12"/>
@@ -18559,7 +18799,7 @@
         <v>2</v>
       </c>
       <c r="L85" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-2</v>
       </c>
       <c r="M85" s="8"/>
@@ -18568,24 +18808,24 @@
         <v>0</v>
       </c>
       <c r="P85" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="S85" s="16"/>
       <c r="T85" s="16"/>
       <c r="U85" s="12" t="e">
+        <f t="shared" si="21"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V85" s="8" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V85" s="8" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
       <c r="W85" s="8">
         <v>0</v>
       </c>
@@ -18620,10 +18860,13 @@
         <v>72</v>
       </c>
       <c r="AH85" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AI85" s="12"/>
+      <c r="AI85" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="AJ85" s="12"/>
       <c r="AK85" s="12"/>
       <c r="AL85" s="12"/>
@@ -18672,7 +18915,7 @@
         <v>40</v>
       </c>
       <c r="L86" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-43</v>
       </c>
       <c r="M86" s="8"/>
@@ -18681,24 +18924,24 @@
         <v>0</v>
       </c>
       <c r="P86" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-0.6</v>
       </c>
       <c r="Q86" s="10"/>
       <c r="R86" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="S86" s="16"/>
       <c r="T86" s="16"/>
       <c r="U86" s="12">
+        <f t="shared" si="21"/>
+        <v>-1.6666666666666667</v>
+      </c>
+      <c r="V86" s="8">
         <f t="shared" si="20"/>
         <v>-1.6666666666666667</v>
       </c>
-      <c r="V86" s="8">
-        <f t="shared" si="19"/>
-        <v>-1.6666666666666667</v>
-      </c>
       <c r="W86" s="8">
         <v>-1.2</v>
       </c>
@@ -18731,10 +18974,13 @@
       </c>
       <c r="AG86" s="8"/>
       <c r="AH86" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AI86" s="12"/>
+      <c r="AI86" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="AJ86" s="12"/>
       <c r="AK86" s="12"/>
       <c r="AL86" s="12"/>
@@ -18785,7 +19031,7 @@
         <v>137</v>
       </c>
       <c r="L87" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M87" s="12"/>
@@ -18794,25 +19040,25 @@
         <v>264</v>
       </c>
       <c r="P87" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>27.4</v>
       </c>
       <c r="Q87" s="4">
-        <f t="shared" ref="Q87:Q88" si="23">15*P87-O87-F87</f>
+        <f t="shared" ref="Q87:Q88" si="25">15*P87-O87-F87</f>
         <v>101</v>
       </c>
       <c r="R87" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>101</v>
       </c>
       <c r="S87" s="16"/>
       <c r="T87" s="16"/>
       <c r="U87" s="12">
+        <f t="shared" si="21"/>
+        <v>15</v>
+      </c>
+      <c r="V87" s="12">
         <f t="shared" si="20"/>
-        <v>15</v>
-      </c>
-      <c r="V87" s="12">
-        <f t="shared" si="19"/>
         <v>11.313868613138686</v>
       </c>
       <c r="W87" s="12">
@@ -18847,10 +19093,13 @@
       </c>
       <c r="AG87" s="12"/>
       <c r="AH87" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>12.12</v>
       </c>
-      <c r="AI87" s="12"/>
+      <c r="AI87" s="12">
+        <f t="shared" si="23"/>
+        <v>3.2879999999999998</v>
+      </c>
       <c r="AJ87" s="12"/>
       <c r="AK87" s="12"/>
       <c r="AL87" s="12"/>
@@ -18899,7 +19148,7 @@
         <v>117</v>
       </c>
       <c r="L88" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-42</v>
       </c>
       <c r="M88" s="12"/>
@@ -18908,11 +19157,11 @@
         <v>160</v>
       </c>
       <c r="P88" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>15</v>
       </c>
       <c r="Q88" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>65</v>
       </c>
       <c r="R88" s="4">
@@ -18927,11 +19176,11 @@
         <v>Задача для ТП</v>
       </c>
       <c r="U88" s="12">
+        <f t="shared" si="21"/>
+        <v>18.666666666666668</v>
+      </c>
+      <c r="V88" s="12">
         <f t="shared" si="20"/>
-        <v>18.666666666666668</v>
-      </c>
-      <c r="V88" s="12">
-        <f t="shared" si="19"/>
         <v>10.666666666666666</v>
       </c>
       <c r="W88" s="12">
@@ -18966,10 +19215,13 @@
       </c>
       <c r="AG88" s="12"/>
       <c r="AH88" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>39.6</v>
       </c>
-      <c r="AI88" s="12"/>
+      <c r="AI88" s="12">
+        <f t="shared" si="23"/>
+        <v>4.95</v>
+      </c>
       <c r="AJ88" s="12"/>
       <c r="AK88" s="12"/>
       <c r="AL88" s="12"/>
@@ -19020,7 +19272,7 @@
         <v>194</v>
       </c>
       <c r="L89" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-104</v>
       </c>
       <c r="M89" s="12"/>
@@ -19029,7 +19281,7 @@
         <v>422</v>
       </c>
       <c r="P89" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>18</v>
       </c>
       <c r="Q89" s="4"/>
@@ -19045,11 +19297,11 @@
         <v>Задача для ТП</v>
       </c>
       <c r="U89" s="12">
+        <f t="shared" si="21"/>
+        <v>37.277777777777779</v>
+      </c>
+      <c r="V89" s="12">
         <f t="shared" si="20"/>
-        <v>37.277777777777779</v>
-      </c>
-      <c r="V89" s="12">
-        <f t="shared" si="19"/>
         <v>23.388888888888889</v>
       </c>
       <c r="W89" s="12">
@@ -19086,10 +19338,13 @@
         <v>107</v>
       </c>
       <c r="AH89" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>37.5</v>
       </c>
-      <c r="AI89" s="12"/>
+      <c r="AI89" s="12">
+        <f t="shared" si="23"/>
+        <v>2.6999999999999997</v>
+      </c>
       <c r="AJ89" s="12"/>
       <c r="AK89" s="12"/>
       <c r="AL89" s="12"/>
@@ -19136,7 +19391,7 @@
         <v>86</v>
       </c>
       <c r="L90" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-97</v>
       </c>
       <c r="M90" s="8"/>
@@ -19145,24 +19400,24 @@
         <v>0</v>
       </c>
       <c r="P90" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-2.2000000000000002</v>
       </c>
       <c r="Q90" s="10"/>
       <c r="R90" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="S90" s="16"/>
       <c r="T90" s="16"/>
       <c r="U90" s="12">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="V90" s="8">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="V90" s="8">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
       <c r="W90" s="8">
         <v>0.2</v>
       </c>
@@ -19197,10 +19452,13 @@
         <v>143</v>
       </c>
       <c r="AH90" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AI90" s="12"/>
+      <c r="AI90" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="AJ90" s="12"/>
       <c r="AK90" s="12"/>
       <c r="AL90" s="12"/>
@@ -19241,7 +19499,7 @@
       <c r="J91" s="8"/>
       <c r="K91" s="8"/>
       <c r="L91" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M91" s="8"/>
@@ -19250,24 +19508,24 @@
         <v>0</v>
       </c>
       <c r="P91" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="S91" s="16"/>
       <c r="T91" s="16"/>
       <c r="U91" s="12" t="e">
+        <f t="shared" si="21"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V91" s="8" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V91" s="8" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
       <c r="W91" s="8">
         <v>0</v>
       </c>
@@ -19302,10 +19560,13 @@
         <v>72</v>
       </c>
       <c r="AH91" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AI91" s="12"/>
+      <c r="AI91" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="AJ91" s="12"/>
       <c r="AK91" s="12"/>
       <c r="AL91" s="12"/>
@@ -19346,7 +19607,7 @@
       <c r="J92" s="8"/>
       <c r="K92" s="8"/>
       <c r="L92" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M92" s="8"/>
@@ -19355,24 +19616,24 @@
         <v>0</v>
       </c>
       <c r="P92" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Q92" s="10"/>
       <c r="R92" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="S92" s="16"/>
       <c r="T92" s="16"/>
       <c r="U92" s="12" t="e">
+        <f t="shared" si="21"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V92" s="8" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V92" s="8" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
       <c r="W92" s="8">
         <v>0</v>
       </c>
@@ -19407,10 +19668,13 @@
         <v>72</v>
       </c>
       <c r="AH92" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AI92" s="12"/>
+      <c r="AI92" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="AJ92" s="12"/>
       <c r="AK92" s="12"/>
       <c r="AL92" s="12"/>
@@ -19461,7 +19725,7 @@
         <v>124</v>
       </c>
       <c r="L93" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>4</v>
       </c>
       <c r="M93" s="12"/>
@@ -19470,25 +19734,25 @@
         <v>100</v>
       </c>
       <c r="P93" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>25.6</v>
       </c>
       <c r="Q93" s="4">
-        <f t="shared" ref="Q93" si="24">15*P93-O93-F93</f>
+        <f t="shared" ref="Q93" si="26">15*P93-O93-F93</f>
         <v>87</v>
       </c>
       <c r="R93" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>87</v>
       </c>
       <c r="S93" s="16"/>
       <c r="T93" s="16"/>
       <c r="U93" s="12">
+        <f t="shared" si="21"/>
+        <v>15</v>
+      </c>
+      <c r="V93" s="12">
         <f t="shared" si="20"/>
-        <v>15</v>
-      </c>
-      <c r="V93" s="12">
-        <f t="shared" si="19"/>
         <v>11.6015625</v>
       </c>
       <c r="W93" s="12">
@@ -19525,10 +19789,13 @@
         <v>44</v>
       </c>
       <c r="AH93" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>34.800000000000004</v>
       </c>
-      <c r="AI93" s="12"/>
+      <c r="AI93" s="12">
+        <f t="shared" si="23"/>
+        <v>10.240000000000002</v>
+      </c>
       <c r="AJ93" s="12"/>
       <c r="AK93" s="12"/>
       <c r="AL93" s="12"/>
@@ -19579,7 +19846,7 @@
         <v>13</v>
       </c>
       <c r="L94" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-5</v>
       </c>
       <c r="M94" s="8"/>
@@ -19588,14 +19855,14 @@
         <v>0</v>
       </c>
       <c r="P94" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1.6</v>
       </c>
       <c r="Q94" s="10">
         <v>0</v>
       </c>
       <c r="R94" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="S94" s="17"/>
@@ -19604,13 +19871,13 @@
         <v xml:space="preserve">нет потребности, позиция заведена для Донецка </v>
       </c>
       <c r="U94" s="12">
+        <f t="shared" si="21"/>
+        <v>5</v>
+      </c>
+      <c r="V94" s="8">
         <f t="shared" si="20"/>
         <v>5</v>
       </c>
-      <c r="V94" s="8">
-        <f t="shared" si="19"/>
-        <v>5</v>
-      </c>
       <c r="W94" s="8">
         <v>2.4</v>
       </c>
@@ -19645,10 +19912,13 @@
         <v>72</v>
       </c>
       <c r="AH94" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AI94" s="12"/>
+      <c r="AI94" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="AJ94" s="12"/>
       <c r="AK94" s="12"/>
       <c r="AL94" s="12"/>
@@ -19689,7 +19959,7 @@
       <c r="J95" s="8"/>
       <c r="K95" s="8"/>
       <c r="L95" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M95" s="8"/>
@@ -19698,24 +19968,24 @@
         <v>0</v>
       </c>
       <c r="P95" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="S95" s="16"/>
       <c r="T95" s="16"/>
       <c r="U95" s="12" t="e">
+        <f t="shared" si="21"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V95" s="8" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V95" s="8" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
       <c r="W95" s="8">
         <v>0</v>
       </c>
@@ -19750,10 +20020,13 @@
         <v>72</v>
       </c>
       <c r="AH95" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AI95" s="12"/>
+      <c r="AI95" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="AJ95" s="12"/>
       <c r="AK95" s="12"/>
       <c r="AL95" s="12"/>
@@ -19794,7 +20067,7 @@
         <v>0.8</v>
       </c>
       <c r="L96" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-0.8</v>
       </c>
       <c r="M96" s="8"/>
@@ -19803,24 +20076,24 @@
         <v>0</v>
       </c>
       <c r="P96" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Q96" s="10"/>
       <c r="R96" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="S96" s="16"/>
       <c r="T96" s="16"/>
       <c r="U96" s="12" t="e">
+        <f t="shared" si="21"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V96" s="8" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V96" s="8" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
       <c r="W96" s="8">
         <v>0</v>
       </c>
@@ -19855,10 +20128,13 @@
         <v>72</v>
       </c>
       <c r="AH96" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AI96" s="12"/>
+      <c r="AI96" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="AJ96" s="12"/>
       <c r="AK96" s="12"/>
       <c r="AL96" s="12"/>
@@ -19909,7 +20185,7 @@
         <v>107</v>
       </c>
       <c r="L97" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-8</v>
       </c>
       <c r="M97" s="12"/>
@@ -19918,25 +20194,25 @@
         <v>169</v>
       </c>
       <c r="P97" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>19.8</v>
       </c>
       <c r="Q97" s="4">
-        <f t="shared" ref="Q97:Q103" si="25">15*P97-O97-F97</f>
+        <f t="shared" ref="Q97:Q103" si="27">15*P97-O97-F97</f>
         <v>117</v>
       </c>
       <c r="R97" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>117</v>
       </c>
       <c r="S97" s="16"/>
       <c r="T97" s="16"/>
       <c r="U97" s="12">
+        <f t="shared" si="21"/>
+        <v>15</v>
+      </c>
+      <c r="V97" s="12">
         <f t="shared" si="20"/>
-        <v>15</v>
-      </c>
-      <c r="V97" s="12">
-        <f t="shared" si="19"/>
         <v>9.0909090909090899</v>
       </c>
       <c r="W97" s="12">
@@ -19971,10 +20247,13 @@
       </c>
       <c r="AG97" s="12"/>
       <c r="AH97" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>38.61</v>
       </c>
-      <c r="AI97" s="12"/>
+      <c r="AI97" s="12">
+        <f t="shared" si="23"/>
+        <v>6.5340000000000007</v>
+      </c>
       <c r="AJ97" s="12"/>
       <c r="AK97" s="12"/>
       <c r="AL97" s="12"/>
@@ -20023,7 +20302,7 @@
         <v>26</v>
       </c>
       <c r="L98" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M98" s="8"/>
@@ -20032,14 +20311,14 @@
         <v>16</v>
       </c>
       <c r="P98" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>5.2</v>
       </c>
       <c r="Q98" s="10">
         <v>0</v>
       </c>
       <c r="R98" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="S98" s="17"/>
@@ -20048,13 +20327,13 @@
         <v xml:space="preserve">нет потребности, данная позиции уходит в уценку </v>
       </c>
       <c r="U98" s="12">
+        <f t="shared" si="21"/>
+        <v>3.0769230769230766</v>
+      </c>
+      <c r="V98" s="8">
         <f t="shared" si="20"/>
         <v>3.0769230769230766</v>
       </c>
-      <c r="V98" s="8">
-        <f t="shared" si="19"/>
-        <v>3.0769230769230766</v>
-      </c>
       <c r="W98" s="8">
         <v>3.2</v>
       </c>
@@ -20089,10 +20368,13 @@
         <v>152</v>
       </c>
       <c r="AH98" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AI98" s="12"/>
+      <c r="AI98" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="AJ98" s="12"/>
       <c r="AK98" s="12"/>
       <c r="AL98" s="12"/>
@@ -20144,7 +20426,7 @@
         <v>37</v>
       </c>
       <c r="L99" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M99" s="12"/>
@@ -20153,25 +20435,25 @@
         <v>0</v>
       </c>
       <c r="P99" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>7.4</v>
       </c>
       <c r="Q99" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>52</v>
       </c>
       <c r="R99" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>52</v>
       </c>
       <c r="S99" s="16"/>
       <c r="T99" s="16"/>
       <c r="U99" s="12">
+        <f t="shared" si="21"/>
+        <v>15</v>
+      </c>
+      <c r="V99" s="12">
         <f t="shared" si="20"/>
-        <v>15</v>
-      </c>
-      <c r="V99" s="12">
-        <f t="shared" si="19"/>
         <v>7.9729729729729728</v>
       </c>
       <c r="W99" s="12">
@@ -20208,10 +20490,13 @@
         <v>153</v>
       </c>
       <c r="AH99" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>5.2</v>
       </c>
-      <c r="AI99" s="12"/>
+      <c r="AI99" s="12">
+        <f t="shared" si="23"/>
+        <v>0.7400000000000001</v>
+      </c>
       <c r="AJ99" s="12"/>
       <c r="AK99" s="12"/>
       <c r="AL99" s="12"/>
@@ -20264,7 +20549,7 @@
         <v>128</v>
       </c>
       <c r="L100" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>46</v>
       </c>
       <c r="M100" s="12"/>
@@ -20273,24 +20558,24 @@
         <v>403</v>
       </c>
       <c r="P100" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>34.799999999999997</v>
       </c>
       <c r="Q100" s="4"/>
       <c r="R100" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="S100" s="16"/>
       <c r="T100" s="16"/>
       <c r="U100" s="12">
+        <f t="shared" si="21"/>
+        <v>18.735632183908049</v>
+      </c>
+      <c r="V100" s="12">
         <f t="shared" si="20"/>
         <v>18.735632183908049</v>
       </c>
-      <c r="V100" s="12">
-        <f t="shared" si="19"/>
-        <v>18.735632183908049</v>
-      </c>
       <c r="W100" s="12">
         <v>53.8</v>
       </c>
@@ -20325,10 +20610,13 @@
         <v>154</v>
       </c>
       <c r="AH100" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AI100" s="12"/>
+      <c r="AI100" s="12">
+        <f t="shared" si="23"/>
+        <v>3.48</v>
+      </c>
       <c r="AJ100" s="12"/>
       <c r="AK100" s="12"/>
       <c r="AL100" s="12"/>
@@ -20380,7 +20668,7 @@
         <v>290</v>
       </c>
       <c r="L101" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-137</v>
       </c>
       <c r="M101" s="12"/>
@@ -20389,24 +20677,24 @@
         <v>216</v>
       </c>
       <c r="P101" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>30.6</v>
       </c>
       <c r="Q101" s="4"/>
       <c r="R101" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="S101" s="16"/>
       <c r="T101" s="16"/>
       <c r="U101" s="12">
+        <f t="shared" si="21"/>
+        <v>25.326797385620914</v>
+      </c>
+      <c r="V101" s="12">
         <f t="shared" si="20"/>
         <v>25.326797385620914</v>
       </c>
-      <c r="V101" s="12">
-        <f t="shared" si="19"/>
-        <v>25.326797385620914</v>
-      </c>
       <c r="W101" s="12">
         <v>63.6</v>
       </c>
@@ -20441,10 +20729,13 @@
         <v>155</v>
       </c>
       <c r="AH101" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AI101" s="12"/>
+      <c r="AI101" s="12">
+        <f t="shared" si="23"/>
+        <v>3.0600000000000005</v>
+      </c>
       <c r="AJ101" s="12"/>
       <c r="AK101" s="12"/>
       <c r="AL101" s="12"/>
@@ -20496,7 +20787,7 @@
         <v>189</v>
       </c>
       <c r="L102" s="12">
-        <f t="shared" ref="L102:L105" si="26">E102-K102</f>
+        <f t="shared" ref="L102:L105" si="28">E102-K102</f>
         <v>-38</v>
       </c>
       <c r="M102" s="12"/>
@@ -20505,24 +20796,24 @@
         <v>243</v>
       </c>
       <c r="P102" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>30.2</v>
       </c>
       <c r="Q102" s="4">
         <v>16</v>
       </c>
       <c r="R102" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>16</v>
       </c>
       <c r="S102" s="16"/>
       <c r="T102" s="16"/>
       <c r="U102" s="12">
+        <f t="shared" si="21"/>
+        <v>15.463576158940398</v>
+      </c>
+      <c r="V102" s="12">
         <f t="shared" si="20"/>
-        <v>15.463576158940398</v>
-      </c>
-      <c r="V102" s="12">
-        <f t="shared" si="19"/>
         <v>14.933774834437086</v>
       </c>
       <c r="W102" s="12">
@@ -20559,10 +20850,13 @@
         <v>156</v>
       </c>
       <c r="AH102" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>6.4</v>
       </c>
-      <c r="AI102" s="12"/>
+      <c r="AI102" s="12">
+        <f t="shared" si="23"/>
+        <v>12.08</v>
+      </c>
       <c r="AJ102" s="12"/>
       <c r="AK102" s="12"/>
       <c r="AL102" s="12"/>
@@ -20611,7 +20905,7 @@
         <v>77</v>
       </c>
       <c r="L103" s="12">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-4</v>
       </c>
       <c r="M103" s="12"/>
@@ -20620,25 +20914,25 @@
         <v>80</v>
       </c>
       <c r="P103" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>14.6</v>
       </c>
       <c r="Q103" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>14</v>
       </c>
       <c r="R103" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>14</v>
       </c>
       <c r="S103" s="16"/>
       <c r="T103" s="16"/>
       <c r="U103" s="12">
+        <f t="shared" si="21"/>
+        <v>15</v>
+      </c>
+      <c r="V103" s="12">
         <f t="shared" si="20"/>
-        <v>15</v>
-      </c>
-      <c r="V103" s="12">
-        <f t="shared" si="19"/>
         <v>14.04109589041096</v>
       </c>
       <c r="W103" s="12">
@@ -20675,10 +20969,13 @@
         <v>107</v>
       </c>
       <c r="AH103" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1.4000000000000001</v>
       </c>
-      <c r="AI103" s="12"/>
+      <c r="AI103" s="12">
+        <f t="shared" si="23"/>
+        <v>1.46</v>
+      </c>
       <c r="AJ103" s="12"/>
       <c r="AK103" s="12"/>
       <c r="AL103" s="12"/>
@@ -20727,7 +21024,7 @@
         <v>79</v>
       </c>
       <c r="L104" s="12">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-1</v>
       </c>
       <c r="M104" s="12"/>
@@ -20736,24 +21033,24 @@
         <v>125</v>
       </c>
       <c r="P104" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>15.6</v>
       </c>
       <c r="Q104" s="4"/>
       <c r="R104" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="S104" s="16"/>
       <c r="T104" s="16"/>
       <c r="U104" s="12">
+        <f t="shared" si="21"/>
+        <v>15.128205128205128</v>
+      </c>
+      <c r="V104" s="12">
         <f t="shared" si="20"/>
         <v>15.128205128205128</v>
       </c>
-      <c r="V104" s="12">
-        <f t="shared" si="19"/>
-        <v>15.128205128205128</v>
-      </c>
       <c r="W104" s="12">
         <v>20</v>
       </c>
@@ -20788,10 +21085,13 @@
         <v>107</v>
       </c>
       <c r="AH104" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AI104" s="12"/>
+      <c r="AI104" s="12">
+        <f t="shared" si="23"/>
+        <v>1.56</v>
+      </c>
       <c r="AJ104" s="12"/>
       <c r="AK104" s="12"/>
       <c r="AL104" s="12"/>
@@ -20830,7 +21130,7 @@
       <c r="J105" s="12"/>
       <c r="K105" s="12"/>
       <c r="L105" s="12">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M105" s="12"/>
@@ -20839,24 +21139,24 @@
         <v>100</v>
       </c>
       <c r="P105" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Q105" s="4"/>
       <c r="R105" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="S105" s="16"/>
       <c r="T105" s="16"/>
       <c r="U105" s="12" t="e">
+        <f t="shared" si="21"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V105" s="12" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V105" s="12" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
       <c r="W105" s="12">
         <v>0</v>
       </c>
@@ -20891,10 +21191,13 @@
         <v>160</v>
       </c>
       <c r="AH105" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AI105" s="12"/>
+      <c r="AI105" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="AJ105" s="12"/>
       <c r="AK105" s="12"/>
       <c r="AL105" s="12"/>
